--- a/Results/MIROCALS_vs_RILUZOLE_Table1.xlsx
+++ b/Results/MIROCALS_vs_RILUZOLE_Table1.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43 (4.6%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -651,7 +651,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>895 (95.4%)</t>
+          <t>938 (100.0%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
